--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -787,18 +787,22 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>v4</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr"/>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>Validée</t>
+          <t>Créée — G4+M5 (polynôme)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Fiche technique NETPLY v4.html</t>
+          <t>Fiches_Netair/Fiche technique NETPLY v6.html</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Seule fiche déjà rédigée — base de référence visuelle · Données alignées sur la fiche v4</t>
+          <t>v6 retravaillée d'après TITAPLY EC (fiche 2018) : specs corrigées (acier galvanisé, sans couture ni colle), éco-conception générique. v1.0 (gabarit) conservée comme ancre d'identité.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -639,28 +639,44 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>G1 / G2</t>
+          <t>G3 (réf.) — gamme G1 → G3</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>ISO Coarse</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
+          <t>Coarse 50%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr"/>
+          <t>Créée — mono-classe G3 (photo placeholder à remplacer)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETMETAL.html</t>
+        </is>
+      </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
           <t>TITAMETAL</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Épaisseurs 25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Épaisseurs 25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer.</t>
+          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Épaisseurs 10/15/20/25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -701,28 +701,44 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>G2 / G3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>ISO Coarse</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
+          <t>Coarse 50%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr"/>
+          <t>Créée — mono-classe G3 (épaisseur &amp; photo à valider)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETFIL.html</t>
+        </is>
+      </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
           <t>TITAFIL</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Mono-classe G3 / Coarse 50% (équivalence indicative). 3 révisions Titanair : descriptif 2015 G2/G3 ; fiche v2_2020 G3 (fibre synthétique) ; v3_2023 G4/Coarse 65% (100% polyester). Choix : G3 cohérent gamme (sous NETPLAN/NETPLY), courbe v2_2020 [2;2,8;4;6,5;11,5;21] à 0,16–1,5 m/s. Polynôme 3,99·v²+7,24·v+0,97 (fit 6 pts, R²≈0,994). Vmax 1,5 (filtre basse vitesse, ventilo-convecteurs), nominal 1,0 m/s (1260 m³/h, ΔP≈12 Pa). Cadre fil acier galvanisé Ø4,5mm. T° 60 °C (acc. 80 °C/1h), feu M1. ÉPAISSEUR 20 mm = À VALIDER (cousu sur mesure). Photo Titanair placeholder (blanc-sur-blanc) à remplacer.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Créée — mono-classe G3 (épaisseur &amp; photo à valider)</t>
+          <t>Créée — mono-classe G3 (photo à remplacer)</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Mono-classe G3 / Coarse 50% (équivalence indicative). 3 révisions Titanair : descriptif 2015 G2/G3 ; fiche v2_2020 G3 (fibre synthétique) ; v3_2023 G4/Coarse 65% (100% polyester). Choix : G3 cohérent gamme (sous NETPLAN/NETPLY), courbe v2_2020 [2;2,8;4;6,5;11,5;21] à 0,16–1,5 m/s. Polynôme 3,99·v²+7,24·v+0,97 (fit 6 pts, R²≈0,994). Vmax 1,5 (filtre basse vitesse, ventilo-convecteurs), nominal 1,0 m/s (1260 m³/h, ΔP≈12 Pa). Cadre fil acier galvanisé Ø4,5mm. T° 60 °C (acc. 80 °C/1h), feu M1. ÉPAISSEUR 20 mm = À VALIDER (cousu sur mesure). Photo Titanair placeholder (blanc-sur-blanc) à remplacer.</t>
+          <t>Mono-classe G3 / Coarse 50% (équivalence indicative). 3 révisions Titanair : descriptif 2015 G2/G3 ; fiche v2_2020 G3 (fibre synthétique) ; v3_2023 G4/Coarse 65% (100% polyester). Choix : G3 cohérent gamme (sous NETPLAN/NETPLY), courbe v2_2020 [2;2,8;4;6,5;11,5;21] à 0,16–1,5 m/s. Polynôme 3,99·v²+7,24·v+0,97 (fit 6 pts, R²≈0,994). Vmax 1,5 (filtre basse vitesse, ventilo-convecteurs), nominal 1,0 m/s (1260 m³/h, ΔP≈12 Pa). Cadre fil acier galvanisé Ø4,5mm. T° 60 °C (acc. 80 °C/1h), feu M1. Profondeur ≈ 4,5 mm (Ø fil du cadre) ; pas de dimensions standard (cousu sur mesure) → bloc dimensions retiré. Photo Titanair placeholder (blanc-sur-blanc) à remplacer.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Épaisseurs 10/15/20/25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer.</t>
+          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Toutes dimensions sur mesure (pas de dimensions standard) ; épaisseurs standard 10/15/20/25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Rouleau media synthétique</t>
+          <t>Média synthétique (panneau découpé)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -771,20 +771,36 @@
           <t>ISO Coarse → ePM10</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr"/>
+          <t>Créée — mono-classe G4 (photo Titanair détourée, à remplacer)</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETFIBRE.html</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
           <t>TITAFIBRE</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 80 °C (acc. 85 °C/1h), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 80 °C (acc. 85 °C/1h), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t>
+          <t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 21/06/2026</t>
+          <t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>v1.0</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>Créée — G4+M5 (polynôme)</t>
+          <t>Validée — G4+M5 (polynôme)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Fiches_Netair/Fiche technique NETPLY v6.html</t>
+          <t>Fiches_Netair/Fiche technique NETPLY.html</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>v6 retravaillée d'après TITAPLY EC (fiche 2018) : specs corrigées (acier galvanisé, sans couture ni colle), éco-conception générique. v1.0 (gabarit) conservée comme ancre d'identité.</t>
+          <t>Fiche officielle (ex-v6) d'après TITAPLY EC : specs réelles, éco-conception. Ancienne fiche placeholder archivée. Ancre test d'identité = produits/_gabarit_ref.json.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -949,28 +949,44 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>G4 → F9</t>
+          <t>M5 → F9 (+ G4)</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>ePM10 → ePM1</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
+          <t>ePM10 50% → ePM1 80%</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr"/>
+          <t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETBAG S.html</t>
+        </is>
+      </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
           <t>TITABAG S</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST_NETBAG.md. Photo Titabag détourée = placeholder.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -984,7 +984,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST_NETBAG.md. Photo Titabag détourée = placeholder.</t>
+          <t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Compacts / poches rigides</t>
+          <t>Filtres compacts (NETPAK)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Compact prisme miniplis</t>
+          <t>Compact à mini-plis prismatiques</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1066,25 +1066,37 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>ePM1 55% / ePM1 70%</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr"/>
+          <t>ePM10 50% → ePM1 80%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr"/>
+          <t>Créée — multi-classes M5→F9 × ép. 48/98 (sélecteur 5 classes, fiche 3 pages)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t>
+        </is>
+      </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>TITAPAK S PRISME</t>
+          <t>TITAPAK S PRISME A</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Nom produit ⚠ à valider</t>
+          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (ep48+ep98). Surface m²/m². Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. PHOTO PLACEHOLDER à remplacer.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>ePM10 50% → ePM1 80%</t>
+          <t>ePM10 50% → ePM1 80% (F7 = ePM1 50% GREENTEX)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (ep48+ep98). Surface m²/m². Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. PHOTO PLACEHOLDER à remplacer.</t>
+          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. PHOTO PLACEHOLDER à remplacer.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1096,7 +1096,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. PHOTO PLACEHOLDER à remplacer.</t>
+          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1096,7 +1096,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme.</t>
+          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Calculateur énergétique indépendant de la courbe (sélecteur efficacité + épaisseur propre). Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>G3 (réf.) — gamme G1 → G3</t>
+          <t>G2 / G3</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Toutes dimensions sur mesure (pas de dimensions standard) ; épaisseurs standard 10/15/20/25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer.</t>
+          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Toutes dimensions sur mesure (pas de dimensions standard) ; épaisseurs standard 10/15/20/25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer. Classe affichée G2 / G3 (déc. PA 22/06/2026 ; courbe réf. G3 mesurée).</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1123,22 +1123,34 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>M5 → F9</t>
+          <t>F7 → F9 (M6 sur demande)</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>ePM10 → ePM1</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
+          <t>ePM1 55% → 80%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr"/>
+          <t>Créée — F7/F8/F9 (moteur série, photo réelle placeholder)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t>
+        </is>
+      </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
           <t>TITAPAK SV GD</t>
@@ -1146,7 +1158,7 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Nom produit ⚠ à valider</t>
+          <t>Compact polydièdre rigide (équiv. TITAPAK SV-GD). 3 classes ePM1 F7/F8/F9, profondeur 292, largeurs 592/490/287. Données réelles caches Excel SV-GD 2018 (F7/F9) + FORMULE_PDC. ⚠ F8 = F9×0,95 (dérivé, affiché normalement sur décision PA, à mesurer). M6 ePM2,5 50% annoncée (livret) sans courbe → specs/badges seulement. Surface média n.c. Parois polystyrène, média PP, séparateurs hot melt, M1, 60°C, EN13053 init+100. DONNEES_PDC l.48-51. Photo SV-GD réelle = placeholder. Détail : CHECKLIST.md.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1185,22 +1185,34 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>M5 → F9</t>
+          <t>F7 → F9</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>ePM10 → ePM1</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
+          <t>ePM1 55% → 80%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr"/>
+          <t>Créée — F7/F8/F9 rechargeable (moteur série, photo placeholder)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t>
+        </is>
+      </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
           <t>TITAPAK S QUARTZ</t>
@@ -1208,7 +1220,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>Argument RSE — cassettes rechargeables. Nom ⚠ à valider</t>
+          <t>Compact polydièdre RECHARGEABLE (équiv. TITAPAK S QUARTZ) — argument RSE (déchets ÷4, cassettes remplacées). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo QUARTZ (Titanair visible) = placeholder.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1006,35 +1006,47 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Compact à brides</t>
+          <t>Panneau compact à brides (DSK)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>M5 → F9</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>ePM10 55% / ePM1 55%</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr"/>
+          <t>ePM1 50% (GREENTEX)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr"/>
+          <t>Créée — mono-classe F7 GREENTEX (photo placeholder)</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t>
+        </is>
+      </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>TITAPAK S D.S.K</t>
+          <t>TITAPAK S DSK (GR)</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>Nom produit ⚠ à valider</t>
+          <t>Panneau compact à brides 100 mm (équiv. TITAPAK S DSK). Décision PA : version GREENTEX (média recyclé, ePM1 50%) car courbe dispo et cohérente — argument éco. Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC (polynôme GREENTEX). Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,46, nominal 3000. Specs fiche HPE DSK 2020 : polystyrène/PP, M1, 60°C, HR 100%, technologie D.S.K (pleine surface sans préfiltre). Variante HPE ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1591,12 +1591,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Combinés</t>
+          <t>Filtres combinés (NETPAK)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Compact particulaire + charbon actif</t>
+          <t>Compact mini-plis + charbon actif</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1606,25 +1606,37 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>ePM1 55% + Moléculaire</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
+          <t>ePM1 50% + CA</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr"/>
+          <t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t>
+        </is>
+      </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>PRISME DUO</t>
+          <t>TITAPAK S PRISME DUO</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>Double filtration. Nom ⚠ à valider</t>
+          <t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1309,28 +1309,44 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>E10 → H14</t>
+          <t>E10 → H14 (EN 1822)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>ISO 35 H</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
+          <t>HEPA / T.H.E</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
+          <t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t>
+        </is>
+      </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>TITACEL V</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1345,32 +1361,44 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>HEPA / T.H.E</t>
+          <t>HEPA / T.H.E (NETPAK)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Filtre laminaire</t>
+          <t>HEPA terminal à flux laminaire</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H14 (EN 1822)</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>ISO 15 U</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr"/>
+          <t>≥ 99,995 % MPPS</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
+          <t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK V LAM.html</t>
+        </is>
+      </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
           <t>TITAPAK V LAM</t>
@@ -1378,7 +1406,7 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Pas de nom signature (volontaire). ⚠ à valider</t>
+          <t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1259,30 +1259,42 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>E10 / H13</t>
+          <t>E10 · H13 (EN 1822)</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>ISO 50 U / ISO 35 H</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
+          <t>HEPA / T.H.E</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr"/>
+          <t>Créée — E10+H13 (mode HEPA)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>TITAPAK V GD</t>
+          <t>TITAPAK V-GD</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Nom produit ⚠ à valider</t>
+          <t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1450,17 +1450,29 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Moléculaire</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr"/>
+          <t>Moléculaire (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
+          <t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t>
+        </is>
+      </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
           <t>PRISME CARB</t>
@@ -1468,7 +1480,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Nom produit ⚠ à valider</t>
+          <t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1512,25 +1512,37 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Moléculaire</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr"/>
+          <t>Moléculaire (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr"/>
+          <t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t>
+        </is>
+      </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>SV GD CARB</t>
+          <t>SV-GD CARB</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Nom produit ⚠ à valider</t>
+          <t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1574,25 +1574,37 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Moléculaire</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
+          <t>Moléculaire (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr"/>
+          <t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t>
+        </is>
+      </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>TITACEL CARB</t>
+          <t>V-CARB (TITACEL CARB)</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Nom produit ⚠ à valider</t>
+          <t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1631,28 +1631,44 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Moléculaire</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
+          <t>ePM1 80% + CA (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>À créer</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr"/>
+          <t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB BAG.html</t>
+        </is>
+      </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr"/>
+          <t>TITABAG F9 CARB</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>ePM10 50% → ePM1 80%</t>
+          <t>G4 · M5 · M6 · F7 · F8 · F9</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder.</t>
+          <t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>NETPAK V LAM</t>
+          <t>NETCEL V LAM</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Fiches_Netair/Fiche technique NETPAK V LAM.html</t>
+          <t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bibliothèque Fiches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bibliothèque Fiches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bibliothèque Fiches'!$A$3:$L$21</definedName>
@@ -825,27 +825,27 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>G4 → M5</t>
+          <t>G4 · M5</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Coarse 65% → ePM10 50%</t>
+          <t>Coarse 65% · ePM10 50%</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>Validée — G4+M5 (polynôme)</t>
+          <t>Validée PA — contenu retravaillé 16/07</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Fiche officielle (ex-v6) d'après TITAPLY EC : specs réelles, éco-conception. Ancienne fiche placeholder archivée. Ancre test d'identité = produits/_gabarit_ref.json.</t>
+          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -897,17 +897,17 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Créée — G4 (photo &amp; ΔP à valider)</t>
+          <t>Validée PA — contenu retravaillé 16/07</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Fiche mono-classe G4 (Coarse 65%, ép. 25 mm), données fiche Titanair 2018. Gamme dispo G2/G3/G4, ép. 8-25 mm. Générée via Generateur/ (≠ système v4/PDC).</t>
+          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -644,22 +644,22 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Coarse 50%</t>
+          <t>Coarse 40% / 50%</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>Créée — mono-classe G3 (photo placeholder à remplacer)</t>
+          <t>Validée PA — contenu retravaillé 17/07</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Mono-classe G3 / Coarse 50% d'après fiche 2018 TITAMETAL KMZ/A (média alu, ép. 48 mm) — FT 2019-037. Doc 2015 annonçait G1-G2 → priorité fiche 2018. Polynôme 7,34·v²+2,44·v+5,57 (fit 5 pts 0,79–2,38 m/s, R²≈1). Vmax 2,4 · nominal 1,5 m/s (1900 m³/h). Toutes dimensions sur mesure (pas de dimensions standard) ; épaisseurs standard 10/15/20/25/30/48 ; variantes galva (KMZ) et inox 304 (KMXCA) sur demande. T° 150 °C (acc. 200 °C/1h), feu M0, régénérable. Photo Titanair détourée = placeholder à remplacer. Classe affichée G2 / G3 (déc. PA 22/06/2026 ; courbe réf. G3 mesurée).</t>
+          <t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -711,17 +711,17 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Créée — mono-classe G3 (photo à remplacer)</t>
+          <t>Validée PA — contenu retravaillé (photo à remplacer)</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Mono-classe G3 / Coarse 50% (équivalence indicative). 3 révisions Titanair : descriptif 2015 G2/G3 ; fiche v2_2020 G3 (fibre synthétique) ; v3_2023 G4/Coarse 65% (100% polyester). Choix : G3 cohérent gamme (sous NETPLAN/NETPLY), courbe v2_2020 [2;2,8;4;6,5;11,5;21] à 0,16–1,5 m/s. Polynôme 3,99·v²+7,24·v+0,97 (fit 6 pts, R²≈0,994). Vmax 1,5 (filtre basse vitesse, ventilo-convecteurs), nominal 1,0 m/s (1260 m³/h, ΔP≈12 Pa). Cadre fil acier galvanisé Ø4,5mm. T° 60 °C (acc. 80 °C/1h), feu M1. Profondeur ≈ 4,5 mm (Ø fil du cadre) ; pas de dimensions standard (cousu sur mesure) → bloc dimensions retiré. Photo Titanair placeholder (blanc-sur-blanc) à remplacer.</t>
+          <t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md.</t>
+          <t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json.</t>
+          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json.</t>
+          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>Panneau compact à brides 100 mm (équiv. TITAPAK S DSK). Décision PA : version GREENTEX (média recyclé, ePM1 50%) car courbe dispo et cohérente — argument éco. Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC (polynôme GREENTEX). Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,46, nominal 3000. Specs fiche HPE DSK 2020 : polystyrène/PP, M1, 60°C, HR 100%, technologie D.S.K (pleine surface sans préfiltre). Variante HPE ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t>
+          <t>Panneau compact à brides 100 mm (équiv. TITAPAK S DSK). Décision PA : version GREENTEX (média recyclé, ePM1 50%) car courbe dispo et cohérente — argument éco. Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC (polynôme GREENTEX). Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,46, nominal 3000. Specs fiche HPE DSK 2020 : polystyrène/PP, M1, 60°C, HR 100%, technologie D.S.K (pleine surface sans préfiltre). Variante HPE ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Calculateur énergétique indépendant de la courbe (sélecteur efficacité + épaisseur propre). Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme.</t>
+          <t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Calculateur énergétique indépendant de la courbe (sélecteur efficacité + épaisseur propre). Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D.</t>
+          <t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -763,27 +763,27 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>G2 → M5</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>ISO Coarse → ePM10</t>
+          <t>Coarse 65%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Créée — mono-classe G4 (photo Titanair détourée, à remplacer)</t>
+          <t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -517,5 +517,5 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souple</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>M5 → F9 (+ G4)</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>F7</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>ePM1 50% (GREENTEX)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX (photo placeholder)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Panneau compact à brides 100 mm (équiv. TITAPAK S DSK). Décision PA : version GREENTEX (média recyclé, ePM1 50%) car courbe dispo et cohérente — argument éco. Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC (polynôme GREENTEX). Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,46, nominal 3000. Specs fiche HPE DSK 2020 : polystyrène/PP, M1, 60°C, HR 100%, technologie D.S.K (pleine surface sans préfiltre). Variante HPE ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50% GREENTEX)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 × ép. 48/98 (sélecteur 5 classes, fiche 3 pages)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Calculateur énergétique indépendant de la courbe (sélecteur efficacité + épaisseur propre). Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique ABS (décl. fabricant, non sourcée), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>F7 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM1 55% → 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Créée — F7/F8/F9 rechargeable (moteur série, photo placeholder)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S QUARTZ</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. TITAPAK S QUARTZ) — argument RSE (déchets ÷4, cassettes remplacées). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo QUARTZ (Titanair visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
+<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souple</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>M5 → F9 (+ G4)</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50% GREENTEX)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 × ép. 48/98 (sélecteur 5 classes, fiche 3 pages)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Calculateur énergétique indépendant de la courbe (sélecteur efficacité + épaisseur propre). Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>F7 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM1 55% → 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Créée — F7/F8/F9 rechargeable (moteur série, photo placeholder)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S QUARTZ</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. TITAPAK S QUARTZ) — argument RSE (déchets ÷4, cassettes remplacées). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo QUARTZ (Titanair visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
 </file>
--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -517,5 +517,5 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souple</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>M5 → F9 (+ G4)</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50% GREENTEX)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 × ép. 48/98 (sélecteur 5 classes, fiche 3 pages)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Cadre acier galvanisé (-A) / plastique (-P). Sources PRISME A HPE 2018 (M5/M6/F8/F9) + GR PRISME A GREENTEX pour F7 (ePM1 50%, ep48+ep98). Surface m²/m². Calculateur énergétique indépendant de la courbe (sélecteur efficacité + épaisseur propre). Pièges : F8=F9 en PRISME P (écarté → PRISME A) ; F9 ep48 = F8+10 Pa (offset suspect) ; F8 ep98 7e pt extrapolé. Photo = TITAPAK PRISME A HD (© A. Périer) détourée sur blanc pur (cadre acier + plissage préservés) — à reshooter sous marque Netair à terme. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>F7 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM1 55% → 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Créée — F7/F8/F9 rechargeable (moteur série, photo placeholder)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S QUARTZ</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. TITAPAK S QUARTZ) — argument RSE (déchets ÷4, cassettes remplacées). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo QUARTZ (Titanair visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
+<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souple</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>M5 → F9 (+ G4)</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>F7 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM1 55% → 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Créée — F7/F8/F9 rechargeable (moteur série, photo placeholder)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S QUARTZ</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. TITAPAK S QUARTZ) — argument RSE (déchets ÷4, cassettes remplacées). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo QUARTZ (Titanair visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
 </file>
--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -517,5 +517,5 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souple</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>M5 → F9 (+ G4)</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>F7 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM1 55% → 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Créée — F7/F8/F9 rechargeable (moteur série, photo placeholder)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S QUARTZ</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. TITAPAK S QUARTZ) — argument RSE (déchets ÷4, cassettes remplacées). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo QUARTZ (Titanair visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
+<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souple</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>M5 → F9 (+ G4)</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (plage M5 → F9, stock F7/F9, courbe 4 500 m³/h, calculateur formats)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S (polydièdre rechargeable)</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. Titanair, polydièdre rechargeable) — argument RSE (réduction des déchets, cassettes remplacées — v1.1 : chiffres ÷4/÷2 adoucis). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo Titanair (marque visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
 </file>
--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -517,5 +517,5 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 (gamme réduite à G4 seul ; photo à remplacer)</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souple</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>M5 → F9 (+ G4)</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Créée — multi-classes M5→F9 (courbe N-séries, photo placeholder)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (plage M5 → F9, stock F7/F9, courbe 4 500 m³/h, calculateur formats)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S (polydièdre rechargeable)</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. Titanair, polydièdre rechargeable) — argument RSE (réduction des déchets, cassettes remplacées — v1.1 : chiffres ÷4/÷2 adoucis). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo Titanair (marque visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
+<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — v1.2 26/07 : vocabulaire « densité progressive » harmonisé (gamme), sous-titre simplifié ; photo à remplacer</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souples</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (plage M5 → F9, stock F7/F9, courbe 4 500 m³/h, calculateur formats)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S (polydièdre rechargeable)</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. Titanair, polydièdre rechargeable) — argument RSE (réduction des déchets, cassettes remplacées — v1.1 : chiffres ÷4/÷2 adoucis). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo Titanair (marque visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
 </file>
--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -517,5 +517,5 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — v1.2 26/07 : vocabulaire « densité progressive » harmonisé (gamme), sous-titre simplifié ; photo à remplacer</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souples</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (plage M5 → F9, stock F7/F9, courbe 4 500 m³/h, calculateur formats)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S (polydièdre rechargeable)</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. Titanair, polydièdre rechargeable) — argument RSE (réduction des déchets, cassettes remplacées — v1.1 : chiffres ÷4/÷2 adoucis). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo Titanair (marque visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Multidièdre T.H.E</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 · H13 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Créée — E10+H13 (mode HEPA)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
+<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — v1.2 26/07 : vocabulaire « densité progressive » harmonisé (gamme), sous-titre simplifié ; photo à remplacer</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souples</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (plage M5 → F9, stock F7/F9, courbe 4 500 m³/h, calculateur formats)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S (polydièdre rechargeable)</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. Titanair, polydièdre rechargeable) — argument RSE (réduction des déchets, cassettes remplacées — v1.1 : chiffres ÷4/÷2 adoucis). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo Titanair (marque visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Filtre absolu multidièdre</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>02/08/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 02/08 (courbe H13 corrigée — axe débit +20 %, DONNEES_PDC réaligné ; plage E10 → H14, H14 sur devis ; nominaux 3000/2500/1500 ; boutique formats standard, classes EPA/HEPA seules)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
 </file>
--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -517,5 +517,1230 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:L21" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="16" customWidth="1" min="1" max="1" /><col width="18" customWidth="1" min="2" max="2" /><col width="24" customWidth="1" min="3" max="3" /><col width="30" customWidth="1" min="4" max="4" /><col width="15" customWidth="1" min="5" max="5" /><col width="22" customWidth="1" min="6" max="6" /><col width="10" customWidth="1" min="7" max="7" /><col width="13" customWidth="1" min="8" max="8" /><col width="14" customWidth="1" min="9" max="9" /><col width="30" customWidth="1" min="10" max="10" /><col width="18" customWidth="1" min="11" max="11" /><col width="34" customWidth="1" min="12" max="12" /></cols><sheetData><row r="1" ht="24" customHeight="1"><c r="A1" s="1" t="inlineStr"><is><t>NETAIR — Bibliothèque des fiches techniques</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t></is></c></row><row r="3" ht="30" customHeight="1"><c r="A3" s="3" t="inlineStr"><is><t>N° FICHE</t></is></c><c r="B3" s="3" t="inlineStr"><is><t>RÉFÉRENCE NETAIR</t></is></c><c r="C3" s="3" t="inlineStr"><is><t>FAMILLE</t></is></c><c r="D3" s="3" t="inlineStr"><is><t>TYPE DE PRODUIT</t></is></c><c r="E3" s="3" t="inlineStr"><is><t>CLASSE EN779</t></is></c><c r="F3" s="3" t="inlineStr"><is><t>CLASSE EN16890</t></is></c><c r="G3" s="3" t="inlineStr"><is><t>VERSION</t></is></c><c r="H3" s="3" t="inlineStr"><is><t>DATE VERSION</t></is></c><c r="I3" s="3" t="inlineStr"><is><t>STATUT FICHE</t></is></c><c r="J3" s="3" t="inlineStr"><is><t>NOM DE FICHIER</t></is></c><c r="K3" s="3" t="inlineStr"><is><t>RÉF. TITANAIR</t></is></c><c r="L3" s="3" t="inlineStr"><is><t>NOTES</t></is></c></row><row r="4"><c r="A4" s="4" t="inlineStr"><is><t>FT-NETMETAL</t></is></c><c r="B4" s="5" t="inlineStr"><is><t>NETMETAL</t></is></c><c r="C4" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D4" s="7" t="inlineStr"><is><t>Cellule filtrante métallique</t></is></c><c r="E4" s="6" t="inlineStr"><is><t>G2 / G3</t></is></c><c r="F4" s="6" t="inlineStr"><is><t>Coarse 40% / 50%</t></is></c><c r="G4" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H4" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I4" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07</t></is></c><c r="J4" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETMETAL.html</t></is></c><c r="K4" s="6" t="inlineStr"><is><t>TITAMETAL</t></is></c><c r="L4" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t></is></c></row><row r="5"><c r="A5" s="4" t="inlineStr"><is><t>FT-NETFIL</t></is></c><c r="B5" s="5" t="inlineStr"><is><t>NETFIL</t></is></c><c r="C5" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D5" s="7" t="inlineStr"><is><t>Cellule filtrante fibres/fil</t></is></c><c r="E5" s="6" t="inlineStr"><is><t>G3</t></is></c><c r="F5" s="6" t="inlineStr"><is><t>Coarse 50%</t></is></c><c r="G5" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H5" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I5" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé (photo à remplacer)</t></is></c><c r="J5" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIL.html</t></is></c><c r="K5" s="6" t="inlineStr"><is><t>TITAFIL</t></is></c><c r="L5" s="7" t="inlineStr"><is><t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t></is></c></row><row r="6"><c r="A6" s="4" t="inlineStr"><is><t>FT-NETFIBRE</t></is></c><c r="B6" s="5" t="inlineStr"><is><t>NETFIBRE</t></is></c><c r="C6" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D6" s="7" t="inlineStr"><is><t>Média synthétique (panneau découpé)</t></is></c><c r="E6" s="6" t="inlineStr"><is><t>G4</t></is></c><c r="F6" s="6" t="inlineStr"><is><t>Coarse 65%</t></is></c><c r="G6" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H6" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I6" s="8" t="inlineStr"><is><t>Validée PA — v1.2 26/07 : vocabulaire « densité progressive » harmonisé (gamme), sous-titre simplifié ; photo à remplacer</t></is></c><c r="J6" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETFIBRE.html</t></is></c><c r="K6" s="6" t="inlineStr"><is><t>TITAFIBRE</t></is></c><c r="L6" s="7" t="inlineStr"><is><t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t></is></c></row><row r="7"><c r="A7" s="10" t="inlineStr"><is><t>FT-NETPLY</t></is></c><c r="B7" s="5" t="inlineStr"><is><t>NETPLY</t></is></c><c r="C7" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D7" s="7" t="inlineStr"><is><t>Filtre plissé</t></is></c><c r="E7" s="6" t="inlineStr"><is><t>G4 · M5</t></is></c><c r="F7" s="6" t="inlineStr"><is><t>Coarse 65% · ePM10 50%</t></is></c><c r="G7" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H7" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I7" s="9" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J7" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPLY.html</t></is></c><c r="K7" s="6" t="inlineStr"><is><t>TITAPLY EC</t></is></c><c r="L7" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="8"><c r="A8" s="4" t="inlineStr"><is><t>FT-NETPLAN</t></is></c><c r="B8" s="5" t="inlineStr"><is><t>NETPLAN</t></is></c><c r="C8" s="6" t="inlineStr"><is><t>Préfiltres</t></is></c><c r="D8" s="7" t="inlineStr"><is><t>Filtre plan standard</t></is></c><c r="E8" s="6" t="inlineStr"><is><t>G2 / G3 / G4</t></is></c><c r="F8" s="6" t="inlineStr"><is><t>Coarse 40% / 50% / 65%</t></is></c><c r="G8" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H8" s="6" t="inlineStr"><is><t>17/07/2026</t></is></c><c r="I8" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 16/07</t></is></c><c r="J8" s="7" t="inlineStr"><is><t>Generateur/Fiche technique NETPLAN.html</t></is></c><c r="K8" s="6" t="inlineStr"><is><t>TITAPLAN</t></is></c><c r="L8" s="7" t="inlineStr"><is><t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t></is></c></row><row r="9"><c r="A9" s="4" t="inlineStr"><is><t>FT-NETBAG-S</t></is></c><c r="B9" s="5" t="inlineStr"><is><t>NETBAG S</t></is></c><c r="C9" s="6" t="inlineStr"><is><t>Poches souples</t></is></c><c r="D9" s="7" t="inlineStr"><is><t>Filtre à poches souples</t></is></c><c r="E9" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F9" s="6" t="inlineStr"><is><t>G4 · M5 · M6 · F7 · F8 · F9</t></is></c><c r="G9" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H9" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I9" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis)</t></is></c><c r="J9" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETBAG S.html</t></is></c><c r="K9" s="6" t="inlineStr"><is><t>TITABAG S</t></is></c><c r="L9" s="7" t="inlineStr"><is><t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t></is></c></row><row r="10"><c r="A10" s="4" t="inlineStr"><is><t>FT-NETPAK-S-BORA</t></is></c><c r="B10" s="5" t="inlineStr"><is><t>NETPAK S BORA</t></is></c><c r="C10" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D10" s="7" t="inlineStr"><is><t>Panneau compact à brides (DSK)</t></is></c><c r="E10" s="6" t="inlineStr"><is><t>G4 → F9</t></is></c><c r="F10" s="6" t="inlineStr"><is><t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G10" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H10" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I10" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t></is></c><c r="J10" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t></is></c><c r="K10" s="6" t="inlineStr"><is><t>TITAPAK S DSK (GR)</t></is></c><c r="L10" s="7" t="inlineStr"><is><t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t></is></c></row><row r="11"><c r="A11" s="4" t="inlineStr"><is><t>FT-NETPAK-S-CILIA</t></is></c><c r="B11" s="5" t="inlineStr"><is><t>NETPAK S CILIA</t></is></c><c r="C11" s="6" t="inlineStr"><is><t>Filtres compacts (NETPAK)</t></is></c><c r="D11" s="7" t="inlineStr"><is><t>Compact à mini-plis prismatiques</t></is></c><c r="E11" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F11" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t></is></c><c r="G11" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H11" s="6" t="inlineStr"><is><t>23/07/2026</t></is></c><c r="I11" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t></is></c><c r="J11" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t></is></c><c r="K11" s="6" t="inlineStr"><is><t>TITAPAK S PRISME A</t></is></c><c r="L11" s="7" t="inlineStr"><is><t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 < M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t></is></c></row><row r="12"><c r="A12" s="4" t="inlineStr"><is><t>FT-NETPAK-S-AZUR</t></is></c><c r="B12" s="5" t="inlineStr"><is><t>NETPAK S AZUR</t></is></c><c r="C12" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D12" s="7" t="inlineStr"><is><t>Polydièdre</t></is></c><c r="E12" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F12" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G12" s="6" t="inlineStr"><is><t>v1.2</t></is></c><c r="H12" s="6" t="inlineStr"><is><t>18/07/2026</t></is></c><c r="I12" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t></is></c><c r="J12" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t></is></c><c r="K12" s="6" t="inlineStr"><is><t>TITAPAK SV GD</t></is></c><c r="L12" s="7" t="inlineStr"><is><t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t></is></c></row><row r="13"><c r="A13" s="4" t="inlineStr"><is><t>FT-NETPAK-S-LUMEN</t></is></c><c r="B13" s="5" t="inlineStr"><is><t>NETPAK S LUMEN</t></is></c><c r="C13" s="6" t="inlineStr"><is><t>Compacts / poches rigides</t></is></c><c r="D13" s="7" t="inlineStr"><is><t>Polydièdre rechargeable</t></is></c><c r="E13" s="6" t="inlineStr"><is><t>M5 → F9</t></is></c><c r="F13" s="6" t="inlineStr"><is><t>ePM10 50% → ePM1 80%</t></is></c><c r="G13" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H13" s="6" t="inlineStr"><is><t>26/07/2026</t></is></c><c r="I13" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 26/07 (plage M5 → F9, stock F7/F9, courbe 4 500 m³/h, calculateur formats)</t></is></c><c r="J13" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t></is></c><c r="K13" s="6" t="inlineStr"><is><t>TITAPAK S (polydièdre rechargeable)</t></is></c><c r="L13" s="7" t="inlineStr"><is><t>Compact polydièdre RECHARGEABLE (équiv. Titanair, polydièdre rechargeable) — argument RSE (réduction des déchets, cassettes remplacées — v1.1 : chiffres ÷4/÷2 adoucis). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo Titanair (marque visible) = placeholder.</t></is></c></row><row r="14"><c r="A14" s="4" t="inlineStr"><is><t>FT-NETCEL-V-AZUR</t></is></c><c r="B14" s="5" t="inlineStr"><is><t>NETCEL V AZUR</t></is></c><c r="C14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D14" s="7" t="inlineStr"><is><t>Filtre absolu multidièdre</t></is></c><c r="E14" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F14" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G14" s="6" t="inlineStr"><is><t>v1.1</t></is></c><c r="H14" s="6" t="inlineStr"><is><t>02/08/2026</t></is></c><c r="I14" s="8" t="inlineStr"><is><t>Validée PA — contenu retravaillé 02/08 (courbe H13 corrigée — axe débit +20 %, DONNEES_PDC réaligné ; plage E10 → H14, H14 sur devis ; nominaux 3000/2500/1500 ; boutique formats standard, classes EPA/HEPA seules)</t></is></c><c r="J14" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t></is></c><c r="K14" s="6" t="inlineStr"><is><t>TITAPAK V-GD</t></is></c><c r="L14" s="7" t="inlineStr"><is><t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t></is></c></row><row r="15"><c r="A15" s="4" t="inlineStr"><is><t>FT-NETCEL-V-NIVAL</t></is></c><c r="B15" s="5" t="inlineStr"><is><t>NETCEL V NIVAL</t></is></c><c r="C15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="D15" s="7" t="inlineStr"><is><t>Filtre polydièdre T.H.E</t></is></c><c r="E15" s="6" t="inlineStr"><is><t>E10 → H14 (EN 1822)</t></is></c><c r="F15" s="6" t="inlineStr"><is><t>HEPA / T.H.E</t></is></c><c r="G15" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H15" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I15" s="8" t="inlineStr"><is><t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t></is></c><c r="J15" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t></is></c><c r="K15" s="6" t="inlineStr"><is><t>TITACEL V</t></is></c><c r="L15" s="7" t="inlineStr"><is><t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t></is></c></row><row r="16"><c r="A16" s="4" t="inlineStr"><is><t>FT-NETPAK-V-LAM</t></is></c><c r="B16" s="5" t="inlineStr"><is><t>NETCEL V LAM</t></is></c><c r="C16" s="6" t="inlineStr"><is><t>HEPA / T.H.E (NETPAK)</t></is></c><c r="D16" s="7" t="inlineStr"><is><t>HEPA terminal à flux laminaire</t></is></c><c r="E16" s="6" t="inlineStr"><is><t>H14 (EN 1822)</t></is></c><c r="F16" s="6" t="inlineStr"><is><t>≥ 99,995 % MPPS</t></is></c><c r="G16" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H16" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I16" s="8" t="inlineStr"><is><t>Créée — mono-classe H14, paradigme HEPA (aref 610², ΔP finale 2×)</t></is></c><c r="J16" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t></is></c><c r="K16" s="6" t="inlineStr"><is><t>TITAPAK V LAM</t></is></c><c r="L16" s="7" t="inlineStr"><is><t>HEPA laminaire H14. Dim. eff. 610×610×68, surface 5,83 m², média fibre de verre, cadre alu, T° 80°C, feu M1. ΔP nom ≈125 Pa @600 m³/h, finale 2× (colmatage ≈400 Pa). 1re fiche moteur en mode HEPA (aref/dim_ref/dp_final_mode x2). Photo placeholder.</t></is></c></row><row r="17"><c r="A17" s="4" t="inlineStr"><is><t>FT-NETCARB-CILIA</t></is></c><c r="B17" s="5" t="inlineStr"><is><t>NETCARB CILIA</t></is></c><c r="C17" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D17" s="7" t="inlineStr"><is><t>Compact charbon actif</t></is></c><c r="E17" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F17" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G17" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H17" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I17" s="8" t="inlineStr"><is><t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t></is></c><c r="J17" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t></is></c><c r="K17" s="6" t="inlineStr"><is><t>PRISME CARB</t></is></c><c r="L17" s="7" t="inlineStr"><is><t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t></is></c></row><row r="18"><c r="A18" s="4" t="inlineStr"><is><t>FT-NETCARB-AZUR</t></is></c><c r="B18" s="5" t="inlineStr"><is><t>NETCARB AZUR</t></is></c><c r="C18" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D18" s="7" t="inlineStr"><is><t>Multidièdre charbon actif</t></is></c><c r="E18" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F18" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G18" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H18" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I18" s="8" t="inlineStr"><is><t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t></is></c><c r="J18" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t></is></c><c r="K18" s="6" t="inlineStr"><is><t>SV-GD CARB</t></is></c><c r="L18" s="7" t="inlineStr"><is><t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t></is></c></row><row r="19"><c r="A19" s="4" t="inlineStr"><is><t>FT-NETCARB-NIVAL</t></is></c><c r="B19" s="5" t="inlineStr"><is><t>NETCARB NIVAL</t></is></c><c r="C19" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D19" s="7" t="inlineStr"><is><t>Polydièdre charbon actif</t></is></c><c r="E19" s="6" t="inlineStr"><is><t>—</t></is></c><c r="F19" s="6" t="inlineStr"><is><t>Moléculaire (ISO 10121)</t></is></c><c r="G19" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H19" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I19" s="8" t="inlineStr"><is><t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t></is></c><c r="J19" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t></is></c><c r="K19" s="6" t="inlineStr"><is><t>V-CARB (TITACEL CARB)</t></is></c><c r="L19" s="7" t="inlineStr"><is><t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t></is></c></row><row r="20"><c r="A20" s="4" t="inlineStr"><is><t>FT-NETCARB-BAG</t></is></c><c r="B20" s="5" t="inlineStr"><is><t>NETCARB BAG</t></is></c><c r="C20" s="6" t="inlineStr"><is><t>Charbon actif</t></is></c><c r="D20" s="7" t="inlineStr"><is><t>Poches charbon actif</t></is></c><c r="E20" s="6" t="inlineStr"><is><t>F9</t></is></c><c r="F20" s="6" t="inlineStr"><is><t>ePM1 80% + CA (ISO 10121)</t></is></c><c r="G20" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H20" s="6" t="inlineStr"><is><t>23/06/2026</t></is></c><c r="I20" s="8" t="inlineStr"><is><t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t></is></c><c r="J20" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETCARB BAG.html</t></is></c><c r="K20" s="6" t="inlineStr"><is><t>TITABAG F9 CARB</t></is></c><c r="L20" s="7" t="inlineStr"><is><t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t></is></c></row><row r="21"><c r="A21" s="4" t="inlineStr"><is><t>FT-NETPAK-S-DUO</t></is></c><c r="B21" s="5" t="inlineStr"><is><t>NETPAK S DUO</t></is></c><c r="C21" s="6" t="inlineStr"><is><t>Filtres combinés (NETPAK)</t></is></c><c r="D21" s="7" t="inlineStr"><is><t>Compact mini-plis + charbon actif</t></is></c><c r="E21" s="6" t="inlineStr"><is><t>F7 + CA</t></is></c><c r="F21" s="6" t="inlineStr"><is><t>ePM1 50% + CA</t></is></c><c r="G21" s="6" t="inlineStr"><is><t>v1.0</t></is></c><c r="H21" s="6" t="inlineStr"><is><t>22/06/2026</t></is></c><c r="I21" s="8" t="inlineStr"><is><t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t></is></c><c r="J21" s="7" t="inlineStr"><is><t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t></is></c><c r="K21" s="6" t="inlineStr"><is><t>TITAPAK S PRISME DUO</t></is></c><c r="L21" s="7" t="inlineStr"><is><t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t></is></c></row></sheetData><autoFilter ref="A3:L21" /><mergeCells count="2"><mergeCell ref="A2:L2" /><mergeCell ref="A1:L1" /></mergeCells><hyperlinks><hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1" /></hyperlinks><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NETAIR — Bibliothèque des fiches techniques</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source de vérité — 1 ligne par version de fiche · N° fiche = FT-&lt;référence&gt; (figé) · Mise à jour : 22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>N° FICHE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>RÉFÉRENCE NETAIR</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>FAMILLE</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>TYPE DE PRODUIT</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>CLASSE EN779</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>CLASSE EN16890</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>VERSION</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>DATE VERSION</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>STATUT FICHE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>NOM DE FICHIER</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>RÉF. TITANAIR</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETMETAL</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>NETMETAL</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Préfiltres</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Cellule filtrante métallique</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>G2 / G3</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Coarse 40% / 50%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 17/07</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETMETAL.html</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>TITAMETAL</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Contenu validé par PA le 17/07/2026 — REPOSITIONNEMENT PRODUIT : présenté comme PARE-GOUTTELETTES (aval batteries froides) puis PARE-ÉTINCELLES (aval batteries électriques), la filtration des particules grossières devenant un usage second. Ce renversement CONTREDIT la doc Titanair 2015 (filtration en usage premier, anti-graisse/séparateur de gouttes en second) : décision PA en tant que fabricant, pas une erreur de lecture. Pare-étincelles et anti-graisse retiré : non sourcés / omis volontairement. Sous-titre « Filtre métallique » (remplace « Cellule filtrante métallique — Préfiltre régénérable ») : seule fiche de la gamme dont le sous-titre n'annonce pas le rôle. ALIGNEMENTS : ISO 16890 avant EN 779 ; ajout du Coarse 40% correspondant au G2 annoncé (il manquait ; sourcé fiches KMX/CA et WZA) ; badge ISO aligné sur le tableau (disait « Coarse 50% » seul) ; « Structure : 2 grilles métalliques » identique à NETPLY/NETPLAN (perte VOLONTAIRE de « fil zingué », pourtant sourcé doc 2015) ; cadre « inox 304 » (disait « inox » seul). DÉROGATIONS ASSUMÉES, ne pas « réparer » : (1) ligne « ΔP finale recommandée » RETIRÉE de la page 1 — seule des 18 fiches, alors que PROCESS.md la dit impérative ; le calculateur p2 applique pourtant toujours +50 Pa (il lit classes.*.add, pas la ligne specs). (2) T° 150 °C maintenue (valeur alu/galva) alors que l'inox 304 tient 200 °C continu / 300 °C acc. (KMX/CA) → variante inox volontairement sous-vendue. Épaisseurs 10/15/20 mm et HR 100 % : confirmées PA en tant que fabricant, NON SOURCÉES. Feu M0 sourcé (les 4 fiches 2018) mais classement français de 1983, remplacé par les Euroclasses EN 13501-1 (A1) + PV d'essai à sécuriser → CHECKLIST. Courbe ΔP agrandie de 21 % (nouveau drapeau courbe_large : 279 → 339 px, la plus grande de la gamme, devant NETPLY à 305). Bouton « Retour au produit » ajouté (charte, 18 fiches). TENSION OUVERTE : le calculateur p2 modélise un colmatage de filtre à particules alors que la p1 présente un pare-gouttelettes. Photo = placeholder Titanair. Détail complet : _arbitrages_pad dans netmetal.json + CHECKLIST.md. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité). Version déjà v1.1 du 17/07 : cohérente, pas de bump nécessaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETFIL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>NETFIL</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Préfiltres</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Cellule filtrante fibres/fil</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Coarse 50%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé (photo à remplacer)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETFIL.html</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>TITAFIL</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Contenu validé par PA le 17/07/2026 (v1.1) — LIRE _arbitrages_pad de produits/netfil.json AVANT toute retouche. Sous-titre « Filtre cousu sur fil » (n'annonce plus le rôle, comme NETMETAL — voulu). Descriptif réécrit, 2 phrases : VC UNIQUEMENT, jamais en CTA (déc. PA, CONTREDIT la doc 2015 qui dit « comme filtre final » en « ventilo-convecteurs, unité de traitement d'air ») ; « filtration finale » retirée, NETFIL classé préfiltre par son efficacité grossière. T° passée à 60 °C (acc. 65 °C/1h) = règle de gamme CLAUDE.md, CONTRE les 4 fiches Titanair qui portent toutes acc. 80 °C. HR « 100 % (sans condensation) » (déc. PA, NON SOURCÉE : aucune fiche TITAFIL n'a de ligne humidité ; l'ancien 95 % ne venait d'aucune source) → même libellé propagé aux 6 fiches à 100 %. ISO 16890 placé avant EN 779 ; « Construction » → « Structure ». SOURCES : 4e révision identifiée le 17/07, TITAFIL.pdf, qui porte « ISO 16890 : COARSE 50% » EN FACE DU G3 → le Coarse 50% est SOURCÉ, pas déduit (le commentaire du JSON affirmait le contraire, corrigé). 4e courbe identifiée : cache 2013 (G3, 6/12/20/38 Pa à 0,5/1/1,5/2 m/s) qui CORROBORE la courbe v2_2020 retenue. ⚠️ RÉSERVES DE CLAUDE ÉCARTÉES PAR PA en connaissance de cause : (a) 3 des 4 points clés sont la recopie de la rubrique « AVANTAGES DES FILTRES » de la plaquette Titanair 2015 (Faible encombrement / Construction renforcée / Toutes dimensions) ; (b) « Faible encombrement » et « Construction renforcée » sont des jugements orphelins depuis la réécriture du descriptif (plus rien sur la page ne les soutient ; une ligne « Épaisseur : 4,5 mm » a été ajoutée puis retirée à la demande de PA). Épaisseur 4,5 mm = DÉDUCTION (Ø du fil du cadre), non sourcée, affichée 3× (légende + calculateur) → CHECKLIST R&amp;D. PROCESS.md disait « 20 mm » : périmé depuis le commit 2454fec du 22/06, corrigé le 17/07. Photo = placeholder Titanair à remplacer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETFIBRE</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>NETFIBRE</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Préfiltres</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Média synthétique (panneau découpé)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Coarse 65%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — v1.2 26/07 : vocabulaire « densité progressive » harmonisé (gamme), sous-titre simplifié ; photo à remplacer</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETFIBRE.html</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>TITAFIBRE</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Mono-classe G4 / Coarse 65% (réf.) d'après fiche 2018 TITAFIBRE G4 (FT 2018-030, ép. 20 mm). Commercialisé en PANNEAU DÉCOUPÉ sur mesure (média aussi en rouleau 20×2 m), pas de tableau dimensions. Courbe ΔP [12;25;41;68] à v[0,5;1;1,5;2] = identique à NETPLAN (probable graphe Excel réutilisé) mais recoupée par doc 2013 (ΔP init G4 38 Pa @1,5 m/s) → retenue. Polynôme 14·v²+1,8·v+8 (fit 4 pts, R²≈0,998). Vmax 2, nominal 1,5 m/s (1900 m³/h, ΔP≈42 Pa). T° 60 °C (acc. 65 °C/1h) — harmonisée NETPLY/NETPLAN, même média (sources Titanair 80/100 °C incohérentes), feu M1, lavable 2-3× (séries G). Gamme complète G2→M5 annoncée (specs+sous-titre) mais courbes G2/G3/M5 à mesurer (1 point doc 2013 : G2 10/G3 24/M5 125 Pa @1,5 m/s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>FT-NETPLY</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>NETPLY</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Préfiltres</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Filtre plissé</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>G4 · M5</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Coarse 65% · ePM10 50%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 16/07</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPLY.html</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>TITAPLY EC</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits ; tableau dimensions fusionné (11→6 lignes, ΔP par classe, références retirées) ; débits nominaux corrigés (1700→1650, 2800→2810, 3050→3030, 2450→2430) ; format 2 pages A4. G3 volontairement absent (pas de marché) alors que Gamme_References_Netair.xlsx annonce G3/G4/M5 → divergence à trancher. Photo = placeholder Titanair. PDF à produire en 2 fichiers (G4, M5). Détail et arbitrages : CHECKLIST.md + _arbitrages_pad dans netply.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETPLAN</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>NETPLAN</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Préfiltres</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Filtre plan standard</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>G2 / G3 / G4</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Coarse 40% / 50% / 65%</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 16/07</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Generateur/Fiche technique NETPLAN.html</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>TITAPLAN</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Contenu validé par PA le 16/07/2026 : descriptif, points clés et caractéristiques réécrits (retrait de « garantit une excellente tenue mécanique » et « longue durée de service », invérifiables). Alignements de gamme : ISO 16890 avant EN 779, « Surface filtrante », classement au feu remonté, média précisé polyester. Débit 287×592 corrigé 900 → 920 m³/h (2,3 % d'écart avec le débit nominal). Note du tableau dimensions purgée de ses chiffres : elle affichait « ≈ 42 Pa » quand la colonne calculait 43. G2/G3 annoncés SANS courbe (seul le G4 est tracé, le graphe G3 Titanair étant une copie du G4) → courbes à mesurer en R&amp;D. « Sans couture ni colle » et « Incinérable » confirmés par PA, non sourcés. Photo = placeholder Titanair. Détail : CHECKLIST.md + _arbitrages_pad dans netplan.json. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA, décision de gamme appliquée à 7 fiches). Valeur NON SOURCÉE (aucune fiche Titanair de ce produit ne porte de ligne humidité).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETBAG-S</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>NETBAG S</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Poches souples</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Filtre à poches souples</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>G4 → F9</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>G4 · M5 · M6 · F7 · F8 · F9</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 26/07 (densité progressive, stock F7 par défaut, courbe/curseur bornés 4 000, boutique code 17 : standard 380/550 chiffrés, G4/M5 et sur-mesure en devis)</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETBAG S.html</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>TITABAG S</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Fiche MULTI-CLASSES (moteur 'series' opt-in). 10 courbes ΔP réelles extraites des courbes vectorielles des PDF TITABAG 2018 (recalées axes ; F9 p500 = contrôle 38..199 Pa). Classes M5/M6/F7/F8/F9 × profondeurs 380/500/550/650 ; surface média réelle par ligne (3,46–6,10 m²). Toutes ePM → ADD +100 Pa. Anomalie M5 550 vs 650 (550 marquée à valider). G4 annoncé (gamme) mais non mesuré. T° 60°C, feu M1, écarteurs thermosoudés sans colle, cadre acier galva/PP ép.25. Données détail : DONNEES_PDC l.28-37. Manques : CHECKLIST.md. Photo Titabag détourée = placeholder. [MAJ 23/06: G4 (Coarse 65%, poche 380, ADD+50) intégré en specs/gamme/badges, SANS courbe — courbe G4 à mesurer (aucune donnée TITABAG/FORMULE_PDC).]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETPAK-S-BORA</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>NETPAK S BORA</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Compacts / poches rigides</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Panneau compact à brides (DSK)</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>G4 → F9</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Coarse 65% → ePM1 80% (F7 = ePM1 50%, média spécial)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 18/07 (plage G4 → F9 affichée, courbe F7 seule ; photo à remplacer)</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S BORA.html</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>TITAPAK S DSK (GR)</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Filtre compact à brides 100 mm (équiv. TITAPAK S DSK). v1.1 18/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Plage G4 → F9 affichée (déc. PA — le doc 2013 ne cite que M5/F7) ; courbe F7 seule, ePM1 50% (média spécial recyclé, PAS 55% ; étiquette du configurateur corrigée via etiquettesIso). Courbe lue sur image GR DSK F7.png, recoupée FORMULE_PDC. Fit 7,16·v²+11,42·v−1,13 (R²=0,9998), mesuré ≤3100 m³/h → Vmax 2,5, nominal 3000, dp 67 Pa. Média « papier polypropylène » (déc. PA ; doc 2013 : microfibre PP), parois « Plastique » (fiche 2020 : polystyrène), bride 25 mm, pas interplis 6 mm (donnée PA non sourcée), M1, 60°C, HR 100% s.c., EN13053. Variante haute efficacité ePM1 55% existe (courbe non exploitable). Surface média n.c. DONNEES_PDC l.55. Photo DSK réelle = placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETPAK-S-CILIA</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>NETPAK S CILIA</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Filtres compacts (NETPAK)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Compact à mini-plis prismatiques</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>M5 → F9</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>ePM10 50% → ePM1 80% (F7 = ePM1 50%, média spécial)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 23/07 (fiche 2 pages, courbe à cases, surfaces m²/m² corrigées ; photo à remplacer)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S CILIA.html</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>TITAPAK S PRISME A</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Filtre compact miniplis (équiv. TITAPAK S PRISME A). v1.1 23/07/2026 : contenu retravaillé validé PA — arbitrages dans _arbitrages_pad du JSON + CHECKLIST.md. Fiche 2 pages (calc_p2) : dimensions en p.1 (dims_pdc : 592×592×48 @3000 · 287×592×48 @1500, ΔP init M5/F7/F9), courbe à cases à cocher (courbe_cases, F7 seule cochée, axe vitesse) + calculateur en p.2 ; tableau ΔP par classe supprimé. ⚠️ SURFACES CORRIGÉES : les valeurs 2018 sont des m²/m² de section (pitch 7,5 mm), pas des m² par cellule — affiché 12,55/25,65 m²/m² (média F7). F7 = ePM1 50% (média spécial). Cadres : acier galvanisé (-A), plastique (-P), cellulose pelliculée (-C, suffixe tranché 23/07 — à tarifer dans l'Excel). Configurateur : étiquette F7 50% via etiquettesIso, 3 cadres même prix, relevé avant/après identique. Réserves R&amp;D : F9 ep48 = F8+10 Pa exact ; F8 ep98 7e pt extrapolé ; croisement F7 48/98 ; F7 &lt; M5/M6. Polynômes DONNEES_PDC l.38-47. Photo PRISME A détourée = placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETPAK-S-AZUR</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>NETPAK S AZUR</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Compacts / poches rigides</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Polydièdre</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>M5 → F9</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>ePM10 50% → ePM1 80%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 17/07 ; v1.2 18/07 : ABS retiré, parois « Plastique » (gamme M5 → F9 ; photo à remplacer)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S AZUR.html</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>TITAPAK SV GD</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Filtre à poches rigides polydièdre (équiv. TITAPAK SV-GD). Gamme M5 → F9 (déc. PA — M5 sans source ni courbe, M6 DEHS sans courbe) ; courbes tracées F7/F8/F9, sans note d'avertissement (déc. PA). ⚠ F8 = arrondi(F9×0,95) 7 pts/7 (dérivé — réserve R&amp;D ROUVERTE 17/07 : l'affirmation antérieure « vraies mesures » était fausse). Courbe jusqu'à 4500 m³/h (extrapolée au-delà de 4000). dp F9 épinglé 95 Pa (mesure ; lissé=96). Média papier PP, parois plastique (ABS retiré 18/07, déc. PA), M1, 60°C, HR 100% s.c., EN13053 init+100. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo SV-GD réelle = placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETPAK-S-LUMEN</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>NETPAK S LUMEN</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Compacts / poches rigides</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Polydièdre rechargeable</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>M5 → F9</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>ePM10 50% → ePM1 80%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 26/07 (plage M5 → F9, stock F7/F9, courbe 4 500 m³/h, calculateur formats)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S LUMEN.html</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>TITAPAK S (polydièdre rechargeable)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Compact polydièdre RECHARGEABLE (équiv. Titanair, polydièdre rechargeable) — argument RSE (réduction des déchets, cassettes remplacées — v1.1 : chiffres ÷4/÷2 adoucis). 3 classes ePM1 F7/F8/F9, profondeur 292. Données réelles courbes vectorielles PDF 2018 (FT 2019-041), cohérentes F7&lt;F8&lt;F9 (pas de piège). Polyester/PP, sans colle ni séparateur (HPE), M1, 60°C, HR 100%, EN13053 init+100. ⚠ Variantes MFILTER/FILTECH 2024-25 divergent → priorité 2018. % ePM1 : livret 60/90 vs fiche 55/80 (retenu). Surface média n.c. DONNEES_PDC l.52-54. Photo Titanair (marque visible) = placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETCEL-V-AZUR</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>NETCEL V AZUR</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>HEPA / T.H.E</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Filtre absolu multidièdre</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>E10 → H14 (EN 1822)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>HEPA / T.H.E</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 02/08 (courbe H13 corrigée — axe débit +20 %, DONNEES_PDC réaligné ; plage E10 → H14, H14 sur devis ; nominaux 3000/2500/1500 ; boutique formats standard, classes EPA/HEPA seules) · 04/08 : « (papier HEPA) » retiré du média (déc. PA) — SANS bump de version, écart assumé</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCEL V AZUR.html</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>TITAPAK V-GD</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Filtre absolu HEPA multidièdre (équiv. TITAPAK V-GD). 592×592×292, média fibre de verre, polyester, M1, 60°C. Mode HEPA (ΔP finale=2×init). Courbes réelles caches Excel : E10 7,16·v²+56,14·v+1,33 (mesuré ≤3500) ; H13 31,80·v²+119,76·v−14,70 (24 m², mesuré ≤2400, extrapolé au-delà). DONNEES_PDC l.57-58. ⚠ Photo = même polydièdre SV-GD que NETPAK S AZUR (placeholder à distinguer). Curseur débit s'init à 3400 (calc OK à 2400).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETCEL-V-NIVAL</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NETCEL V NIVAL</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>HEPA / T.H.E</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Filtre polydièdre T.H.E</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>E10 → H14 (EN 1822)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>HEPA / T.H.E</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCEL V NIVAL.html</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>TITACEL V</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETCEL-V-LAM</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>NETCEL V LAM</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>HEPA / T.H.E</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Filtre à flux laminaire</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>E11 → U15 (EN 1822)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>EPA / HEPA / ULPA</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Validée PA — contenu retravaillé 04/08 (sous-titre « Filtre à flux laminaire » ; 6 formats à vitesse constante ; surface média retirée ; humidité ajoutée ; plage E11 → U15 ouverte à la boutique ; épaisseur 68 mm corrigée dans l'Excel tarifaire)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCEL V LAM.html</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>TITAPAK V LAM</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Filtre à flux laminaire H14 (équiv. TITAPAK V LAM), moteur mono-classe, mode HEPA (ΔP finale = 2×init, dp_final_mode x2). Polynôme 97,91·v²+263,287·v−12,4 (R²=0,9999) ; ΔP ≈125 Pa @600 m³/h (0,4479 m/s) — nominal corroboré par Camfil Megalam ProSafe MD (610×610×66 : 600 m³/h / 140 Pa). Média fibre de verre, cadre alu, séparateur hot melt, M1, 80 °C (acc. 85/1h — ÉCART ASSUMÉ vs AZUR 60 °C, justifié par le cadre alu ; T° d'AZUR à rouvrir). Tableau : 6 formats, débits proportionnels (150→2400 m³/h), sans surface ni référence, en-tête « Efficacité EN 1822 », classe d'abord. Courbe en VITESSE (écart assumé à la convention « axe débit » : 6 formats de 1 à 16 en débit), axe Y 160 Pa. ⚠ Boutique ouverte à E11/E12/H13/U15 SANS courbe ΔP mesurée (U15 = ULPA) ; humidité 100 % non sourcée ; hot melt à 80 °C non vérifié. Arbitrages : _arbitrages_pad du JSON + CHECKLIST.md. Photo placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETCARB-CILIA</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>NETCARB CILIA</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Charbon actif</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Compact charbon actif</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Moléculaire (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Créée — filtre moléculaire charbon actif, 2 épaisseurs 48/98 mm</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB CILIA.html</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>PRISME CARB</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Charbon actif pur (gaz) : pas de classe ePM. ISO 10121 (LD/MD/HD à déterminer). ΔP réelles caches Excel 48/98 (cohérentes 48&gt;98), poly 7 pts. ΔP non colmatante (remplacement à saturation, capacité 15% masse). T° 40°C, HR 50%, feu NA. Nouveaux drapeaux moteur deux_epaisseurs + dp_final_mode:const. Photo CARB.png (grains) placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETCARB-AZUR</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>NETCARB AZUR</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Charbon actif</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Multidièdre charbon actif</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Moléculaire (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Créée — charbon actif poches rigides/dièdre, mono-classe 292 mm</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB AZUR.html</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>SV-GD CARB</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Charbon pur (gaz), pas de classe ePM. Courbe 2020 QL-CARB (8,073·v²+13,383·v+2,929 ; ΔP@3400≈98). Piège 2023 F7=F8=base écarté. Parois POLYESTER, feu NA, T° 40°C (efficacité), HR 70%. Combinable F7/F9 option. Capacité adsorption n.c.→R&amp;D. Photo CARB_BLEND placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETCARB-NIVAL</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>NETCARB NIVAL</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Charbon actif</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Polydièdre charbon actif</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Moléculaire (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Créée — charbon actif polydièdre, mono-classe 292 mm (courbe partagée AZUR)</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB NIVAL.html</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>V-CARB (TITACEL CARB)</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Polydièdre charbon (gaz). ⚠ Aucune courbe ΔP V-CARB mesurée → courbe pack charbon 292 mm de SV-GD/QL partagée (à mesurer R&amp;D). Nominal 3000, ΔP@3000≈80. Combinable F7. T° 40°C, HR 70%, feu NA. Parois polyester à confirmer. Photo Q-carb (code visible→remplacer). Classe LD/MD/HD &amp; capacité→R&amp;D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETCARB-BAG</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>NETCARB BAG</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Charbon actif</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Poches charbon actif</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>ePM1 80% + CA (ISO 10121)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Créée — poches souples F9 à charbon imprégné (combiné), mono-classe 520</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETCARB BAG.html</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>TITABAG F9 CARB</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>COMBINÉ particules+charbon (≠ charbon grains) : classe ISO 16890 F9 ePM1 80% PRIMAIRE + charbon imprégné (odeurs/COV, capacité 15%). COLMATANT → règle ePM +100 (pas const). 9,172·v²+64,135·v−10,429 ; ΔP@3400≈229. Cadre acier, 520mm, T° 40°C, feu NA. HR n.c. Photo forme poches NETBAG placeholder (média imprégné à reshooter).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>FT-NETPAK-S-DUO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NETPAK S DUO</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Filtres combinés (NETPAK)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Compact mini-plis + charbon actif</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>F7 + CA</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>ePM1 50% + CA</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Créée — mono-classe F7 GREENTEX + charbon actif (ep48)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Fiches_Netair/Fiche technique NETPAK S DUO.html</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>TITAPAK S PRISME DUO</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>F7 GREENTEX + charbon actif. ΔP combinée 36→247 Pa (nom 190). Feu NA (charbon non classé). Surface média dév. ≈12,55 m². ΔP finale +100 Pa (= règle Titanair PDC init+100). Photo placeholder PRISME A à remplacer. Capacité CA (grammage) non communiquée → R&amp;D. MAJ 17/07/2026 : libellé humidité passé à « 100 % (sans condensation) » (déc. PA). ⚠️ VERSION VOLONTAIREMENT NON BUMPÉE (reste v1.0) : la passe de contenu de cette fiche n'a pas eu lieu, bumper en v1.1 consommerait le numéro qu'elle mérite. Décision PA du 17/07. La fiche affiche donc « v1.0 — 22/06/2026 » alors que sa ligne humidité date du 17/07 — écart connu et assumé.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:L21"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1331,17 +1331,17 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.1</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Créée — H13 (mode HEPA, E10/H14 courbes à ajouter)</t>
+          <t>Contenu retravaillé v1.1 — courbes E10 + H13 réelles, 4 formats, cadre 610×610 corrigé (H14 à mesurer)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Filtre absolu HEPA polydièdre (équiv. TITACEL V). 610×610×292, surface 40 m², média fibre de verre, M1, 60°C. Mode HEPA (ΔP finale=2×init, EN 1822 ; pas d'étiquette Eurovent). Courbe H13 réelle (cache Excel, fit 9,44·v²+75,31·v−1,20 R²≈1, ΔP@3400≈270). E10 (Excel sans cache) et H14 (courbe = copie exacte du H13, piège) annoncés mais SANS courbe → à mesurer. ⚠ 610×610 sur moteur 592×592 (axe vitesse cosmétique). DONNEES_PDC l.56. Photo TITACEL V réelle = placeholder.</t>
+          <t>Filtre absolu polydièdre (équiv. TITACEL V, aussi TITAPAK V CU). Cadres 610×610 · 592×592 · 610×305 · 592×287, tous en 292 mm ; surface 40 m² pour le 610×610. Média microfibres de verre, parois plastique (acier galvanisé = décision fabricant, non sourcée), M1, 60 °C. Mode HEPA (ΔP finale = 2 × initiale, EN 1822). Courbes RÉELLES E10 et H13 (caches Excel 2018 recoupés au PDF) ; H14 vendu SANS courbe (source = copie exacte du H13, inexploitable), E11/E12 sans courbe. Surface frontale de référence corrigée à 610×610 dans le moteur le 15/08/2026. Arbitrages PA dans _arbitrages_pad du JSON.</t>
         </is>
       </c>
     </row>

--- a/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
+++ b/fiches-techniques/Bibliotheque_Fiches_Techniques_Netair.xlsx
@@ -1269,17 +1269,17 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Validée PA — contenu retravaillé 02/08 (courbe H13 corrigée — axe débit +20 %, DONNEES_PDC réaligné ; plage E10 → H14, H14 sur devis ; nominaux 3000/2500/1500 ; boutique formats standard, classes EPA/HEPA seules) · 04/08 : « (papier HEPA) » retiré du média (déc. PA) — SANS bump de version, écart assumé</t>
+          <t>Contenu retravaillé v1.1 (02/08) — v1.2 (15/08) : ligne « Séparateur : Hot melt » ajoutée (accord PA)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
